--- a/artfynd/A 50668-2024 artfynd.xlsx
+++ b/artfynd/A 50668-2024 artfynd.xlsx
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121408657</v>
+        <v>121407533</v>
       </c>
       <c r="B4" t="n">
-        <v>91093</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,41 +935,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
+          <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>365180</v>
+        <v>365317</v>
       </c>
       <c r="R4" t="n">
-        <v>6619346</v>
+        <v>6619465</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
+          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121407533</v>
+        <v>121405497</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>92008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,37 +1046,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>365317</v>
+        <v>365245</v>
       </c>
       <c r="R5" t="n">
-        <v>6619465</v>
+        <v>6619399</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,14 +1112,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1139,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121405497</v>
+        <v>121408657</v>
       </c>
       <c r="B6" t="n">
-        <v>92008</v>
+        <v>91093</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,50 +1163,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Vrm</t>
+          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>365245</v>
+        <v>365180</v>
       </c>
       <c r="R6" t="n">
-        <v>6619399</v>
+        <v>6619346</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,19 +1224,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,12 +1246,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 50668-2024 artfynd.xlsx
+++ b/artfynd/A 50668-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121405184</v>
+        <v>121405800</v>
       </c>
       <c r="B2" t="n">
-        <v>94700</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Vrm</t>
+          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>365286</v>
+        <v>365028</v>
       </c>
       <c r="R2" t="n">
-        <v>6619406</v>
+        <v>6619257</v>
       </c>
       <c r="S2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
+          <t>Hack i torraka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121405800</v>
+        <v>121408657</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>91105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,43 +809,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
+          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>365028</v>
+        <v>365180</v>
       </c>
       <c r="R3" t="n">
-        <v>6619257</v>
+        <v>6619346</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,24 +870,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack i torraka</t>
+          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121407533</v>
+        <v>121405497</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>92020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,37 +920,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>365317</v>
+        <v>365245</v>
       </c>
       <c r="R4" t="n">
-        <v>6619465</v>
+        <v>6619399</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,14 +986,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121405497</v>
+        <v>121407533</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,46 +1041,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>365245</v>
+        <v>365317</v>
       </c>
       <c r="R5" t="n">
-        <v>6619399</v>
+        <v>6619465</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,19 +1098,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121408657</v>
+        <v>121405184</v>
       </c>
       <c r="B6" t="n">
-        <v>91093</v>
+        <v>94712</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,37 +1148,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4217</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
+          <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>365180</v>
+        <v>365286</v>
       </c>
       <c r="R6" t="n">
-        <v>6619346</v>
+        <v>6619406</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,14 +1214,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
+          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50668-2024 artfynd.xlsx
+++ b/artfynd/A 50668-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121405800</v>
+        <v>121408657</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>91106</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
+          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>365028</v>
+        <v>365180</v>
       </c>
       <c r="R2" t="n">
-        <v>6619257</v>
+        <v>6619346</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,24 +748,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack i torraka</t>
+          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121408657</v>
+        <v>121405184</v>
       </c>
       <c r="B3" t="n">
-        <v>91105</v>
+        <v>94713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,37 +798,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
+          <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>365180</v>
+        <v>365286</v>
       </c>
       <c r="R3" t="n">
-        <v>6619346</v>
+        <v>6619406</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,14 +864,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
+          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121405497</v>
+        <v>121407533</v>
       </c>
       <c r="B4" t="n">
-        <v>92020</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,46 +924,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>365245</v>
+        <v>365317</v>
       </c>
       <c r="R4" t="n">
-        <v>6619399</v>
+        <v>6619465</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,19 +981,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,19 +1003,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121407533</v>
+        <v>121405800</v>
       </c>
       <c r="B5" t="n">
         <v>57367</v>
@@ -1059,19 +1049,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Vrm</t>
+          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>365317</v>
+        <v>365028</v>
       </c>
       <c r="R5" t="n">
-        <v>6619465</v>
+        <v>6619257</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,14 +1093,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
+          <t>Hack i torraka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121405184</v>
+        <v>121405497</v>
       </c>
       <c r="B6" t="n">
-        <v>94712</v>
+        <v>92021</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,25 +1149,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1172,7 +1177,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1181,13 +1186,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>365286</v>
+        <v>365245</v>
       </c>
       <c r="R6" t="n">
-        <v>6619406</v>
+        <v>6619399</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,12 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,12 +1246,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 50668-2024 artfynd.xlsx
+++ b/artfynd/A 50668-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121408657</v>
+        <v>121407533</v>
       </c>
       <c r="B2" t="n">
-        <v>91106</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
+          <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>365180</v>
+        <v>365317</v>
       </c>
       <c r="R2" t="n">
-        <v>6619346</v>
+        <v>6619465</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
+          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121405184</v>
+        <v>121405800</v>
       </c>
       <c r="B3" t="n">
-        <v>94713</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,50 +794,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Vrm</t>
+          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>365286</v>
+        <v>365028</v>
       </c>
       <c r="R3" t="n">
-        <v>6619406</v>
+        <v>6619257</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
+          <t>Hack i torraka</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121407533</v>
+        <v>121405184</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>94716</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,41 +916,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>365317</v>
+        <v>365286</v>
       </c>
       <c r="R4" t="n">
-        <v>6619465</v>
+        <v>6619406</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,14 +986,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
+          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121405800</v>
+        <v>121405497</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>92024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,42 +1046,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
+          <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>365028</v>
+        <v>365245</v>
       </c>
       <c r="R5" t="n">
-        <v>6619257</v>
+        <v>6619399</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,12 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack i torraka</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1139,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121405497</v>
+        <v>121408657</v>
       </c>
       <c r="B6" t="n">
-        <v>92021</v>
+        <v>91109</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,50 +1163,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Vrm</t>
+          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>365245</v>
+        <v>365180</v>
       </c>
       <c r="R6" t="n">
-        <v>6619399</v>
+        <v>6619346</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,19 +1224,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,12 +1246,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 50668-2024 artfynd.xlsx
+++ b/artfynd/A 50668-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121407533</v>
+        <v>121405497</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>92024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>365317</v>
+        <v>365245</v>
       </c>
       <c r="R2" t="n">
-        <v>6619465</v>
+        <v>6619399</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,14 +757,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121405800</v>
+        <v>121408657</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>91109</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,43 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
+          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>365028</v>
+        <v>365180</v>
       </c>
       <c r="R3" t="n">
-        <v>6619257</v>
+        <v>6619346</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,24 +869,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack i torraka</t>
+          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121405184</v>
+        <v>121407533</v>
       </c>
       <c r="B4" t="n">
-        <v>94716</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,50 +915,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>365286</v>
+        <v>365317</v>
       </c>
       <c r="R4" t="n">
-        <v>6619406</v>
+        <v>6619465</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,24 +976,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
+          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121405497</v>
+        <v>121405800</v>
       </c>
       <c r="B5" t="n">
-        <v>92024</v>
+        <v>57370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,46 +1026,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Vrm</t>
+          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>365245</v>
+        <v>365028</v>
       </c>
       <c r="R5" t="n">
-        <v>6619399</v>
+        <v>6619257</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack i torraka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121408657</v>
+        <v>121405184</v>
       </c>
       <c r="B6" t="n">
-        <v>91109</v>
+        <v>94716</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,37 +1148,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4217</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
+          <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>365180</v>
+        <v>365286</v>
       </c>
       <c r="R6" t="n">
-        <v>6619346</v>
+        <v>6619406</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,14 +1214,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
+          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50668-2024 artfynd.xlsx
+++ b/artfynd/A 50668-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121405497</v>
+        <v>121405184</v>
       </c>
       <c r="B2" t="n">
-        <v>92024</v>
+        <v>94722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>365245</v>
+        <v>365286</v>
       </c>
       <c r="R2" t="n">
-        <v>6619399</v>
+        <v>6619406</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121408657</v>
+        <v>121405497</v>
       </c>
       <c r="B3" t="n">
-        <v>91109</v>
+        <v>92030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +813,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
+          <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>365180</v>
+        <v>365245</v>
       </c>
       <c r="R3" t="n">
-        <v>6619346</v>
+        <v>6619399</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,14 +883,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,12 +910,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -906,7 +925,7 @@
         <v>121407533</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1013,7 +1032,7 @@
         <v>121405800</v>
       </c>
       <c r="B5" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1132,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121405184</v>
+        <v>121408657</v>
       </c>
       <c r="B6" t="n">
-        <v>94716</v>
+        <v>91115</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,46 +1167,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Vrm</t>
+          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>365286</v>
+        <v>365180</v>
       </c>
       <c r="R6" t="n">
-        <v>6619406</v>
+        <v>6619346</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,24 +1224,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
+          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50668-2024 artfynd.xlsx
+++ b/artfynd/A 50668-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121405184</v>
+        <v>121405800</v>
       </c>
       <c r="B2" t="n">
-        <v>94722</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Vrm</t>
+          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>365286</v>
+        <v>365028</v>
       </c>
       <c r="R2" t="n">
-        <v>6619406</v>
+        <v>6619257</v>
       </c>
       <c r="S2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
+          <t>Hack i torraka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +785,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -804,7 +800,7 @@
         <v>121405497</v>
       </c>
       <c r="B3" t="n">
-        <v>92030</v>
+        <v>92031</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -925,7 +921,7 @@
         <v>121407533</v>
       </c>
       <c r="B4" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1029,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121405800</v>
+        <v>121408657</v>
       </c>
       <c r="B5" t="n">
-        <v>57371</v>
+        <v>91116</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,43 +1037,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
+          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>365028</v>
+        <v>365180</v>
       </c>
       <c r="R5" t="n">
-        <v>6619257</v>
+        <v>6619346</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,24 +1098,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hack i torraka</t>
+          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121408657</v>
+        <v>121405184</v>
       </c>
       <c r="B6" t="n">
-        <v>91115</v>
+        <v>94723</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,37 +1148,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4217</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
+          <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>365180</v>
+        <v>365286</v>
       </c>
       <c r="R6" t="n">
-        <v>6619346</v>
+        <v>6619406</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,14 +1214,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
+          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50668-2024 artfynd.xlsx
+++ b/artfynd/A 50668-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121405800</v>
+        <v>121405497</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>92031</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
+          <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>365028</v>
+        <v>365245</v>
       </c>
       <c r="R2" t="n">
-        <v>6619257</v>
+        <v>6619399</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack i torraka</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121405497</v>
+        <v>121405184</v>
       </c>
       <c r="B3" t="n">
-        <v>92031</v>
+        <v>94723</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,7 +836,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>365245</v>
+        <v>365286</v>
       </c>
       <c r="R3" t="n">
-        <v>6619399</v>
+        <v>6619406</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +890,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,22 +910,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121407533</v>
+        <v>121408657</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>91116</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,41 +934,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Vrm</t>
+          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>365317</v>
+        <v>365180</v>
       </c>
       <c r="R4" t="n">
-        <v>6619465</v>
+        <v>6619346</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +1002,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
+          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121408657</v>
+        <v>121405800</v>
       </c>
       <c r="B5" t="n">
-        <v>91116</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,38 +1041,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
+          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>365180</v>
+        <v>365028</v>
       </c>
       <c r="R5" t="n">
-        <v>6619346</v>
+        <v>6619257</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,14 +1107,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
+          <t>Hack i torraka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1139,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121405184</v>
+        <v>121407533</v>
       </c>
       <c r="B6" t="n">
-        <v>94723</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,50 +1163,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>365286</v>
+        <v>365317</v>
       </c>
       <c r="R6" t="n">
-        <v>6619406</v>
+        <v>6619465</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,24 +1224,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
+          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50668-2024 artfynd.xlsx
+++ b/artfynd/A 50668-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121405497</v>
+        <v>121405800</v>
       </c>
       <c r="B2" t="n">
-        <v>92031</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Vrm</t>
+          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>365245</v>
+        <v>365028</v>
       </c>
       <c r="R2" t="n">
-        <v>6619399</v>
+        <v>6619257</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hack i torraka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,12 +785,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1029,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121405800</v>
+        <v>121407533</v>
       </c>
       <c r="B5" t="n">
         <v>57372</v>
@@ -1063,24 +1064,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
+          <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>365028</v>
+        <v>365317</v>
       </c>
       <c r="R5" t="n">
-        <v>6619257</v>
+        <v>6619465</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,24 +1103,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hack i torraka</t>
+          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121407533</v>
+        <v>121405497</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>92031</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,37 +1153,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>365317</v>
+        <v>365245</v>
       </c>
       <c r="R6" t="n">
-        <v>6619465</v>
+        <v>6619399</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,14 +1219,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,12 +1246,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 50668-2024 artfynd.xlsx
+++ b/artfynd/A 50668-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121405800</v>
+        <v>121407533</v>
       </c>
       <c r="B2" t="n">
         <v>57372</v>
@@ -709,24 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
+          <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>365028</v>
+        <v>365317</v>
       </c>
       <c r="R2" t="n">
-        <v>6619257</v>
+        <v>6619465</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,24 +748,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack i torraka</t>
+          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121405184</v>
+        <v>121408657</v>
       </c>
       <c r="B3" t="n">
-        <v>94723</v>
+        <v>91116</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,46 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Vrm</t>
+          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>365286</v>
+        <v>365180</v>
       </c>
       <c r="R3" t="n">
-        <v>6619406</v>
+        <v>6619346</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,24 +855,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
+          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121408657</v>
+        <v>121405497</v>
       </c>
       <c r="B4" t="n">
-        <v>91116</v>
+        <v>92031</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,41 +901,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster-Högvalta, Öster-Högvalta, Vrm</t>
+          <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>365180</v>
+        <v>365245</v>
       </c>
       <c r="R4" t="n">
-        <v>6619346</v>
+        <v>6619399</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,14 +971,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Precis norr om en mycket stor rotvält. Precis öst om gamla skogsmaskins stigen. På ett stående träd.</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,22 +998,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121407533</v>
+        <v>121405184</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>94723</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,41 +1022,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>365317</v>
+        <v>365286</v>
       </c>
       <c r="R5" t="n">
-        <v>6619465</v>
+        <v>6619406</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,14 +1092,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
+          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121405497</v>
+        <v>121405800</v>
       </c>
       <c r="B6" t="n">
-        <v>92031</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,46 +1152,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Vrm</t>
+          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>365245</v>
+        <v>365028</v>
       </c>
       <c r="R6" t="n">
-        <v>6619399</v>
+        <v>6619257</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1226,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack i torraka</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,12 +1246,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 50668-2024 artfynd.xlsx
+++ b/artfynd/A 50668-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121407533</v>
+        <v>121405184</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>94731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>365317</v>
+        <v>365286</v>
       </c>
       <c r="R2" t="n">
-        <v>6619465</v>
+        <v>6619406</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,14 +757,24 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
+          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +804,7 @@
         <v>121408657</v>
       </c>
       <c r="B3" t="n">
-        <v>91116</v>
+        <v>91124</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121405497</v>
+        <v>121405800</v>
       </c>
       <c r="B4" t="n">
-        <v>92031</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,46 +924,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stordalen, Stordalen, Vrm</t>
+          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>365245</v>
+        <v>365028</v>
       </c>
       <c r="R4" t="n">
-        <v>6619399</v>
+        <v>6619257</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack i torraka</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,22 +1018,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Joel Norberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121405184</v>
+        <v>121405497</v>
       </c>
       <c r="B5" t="n">
-        <v>94723</v>
+        <v>92039</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1042,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1050,7 +1070,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1059,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>365286</v>
+        <v>365245</v>
       </c>
       <c r="R5" t="n">
-        <v>6619406</v>
+        <v>6619399</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,12 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På rot delen av ett fällt gran med mycket mossa på. Halvvägs uppför "berget"/slänten.</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,22 +1139,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121405800</v>
+        <v>121407533</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,24 +1185,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarnbråten, Kvarnbråten, Vrm</t>
+          <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>365028</v>
+        <v>365317</v>
       </c>
       <c r="R6" t="n">
-        <v>6619257</v>
+        <v>6619465</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,24 +1224,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hack i torraka</t>
+          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,12 +1246,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Norberg</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 50668-2024 artfynd.xlsx
+++ b/artfynd/A 50668-2024 artfynd.xlsx
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121405497</v>
+        <v>121407533</v>
       </c>
       <c r="B5" t="n">
-        <v>92039</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,46 +1046,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>365245</v>
+        <v>365317</v>
       </c>
       <c r="R5" t="n">
-        <v>6619399</v>
+        <v>6619465</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,19 +1103,14 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121407533</v>
+        <v>121405497</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>92039</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,37 +1153,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stordalen, Stordalen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>365317</v>
+        <v>365245</v>
       </c>
       <c r="R6" t="n">
-        <v>6619465</v>
+        <v>6619399</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,14 +1219,19 @@
           <t>2024-11-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spillkråks hål. På ett grovt stående dött träd med sotticka längst ner.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,12 +1246,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 50668-2024 artfynd.xlsx
+++ b/artfynd/A 50668-2024 artfynd.xlsx
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
